--- a/input/mapping/012. OCB_GOLD_TCKH_V_LNSCHD_AVY_BAOANH.xlsx
+++ b/input/mapping/012. OCB_GOLD_TCKH_V_LNSCHD_AVY_BAOANH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/ANHPB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1973" documentId="11_B470716E63316255539532FE5EF52BF8D9823023" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F0D66FF-E6B0-4494-B52D-4EA68DDF5342}"/>
+  <xr:revisionPtr revIDLastSave="2118" documentId="11_B470716E63316255539532FE5EF52BF8D9823023" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C18A35A7-5F3F-4D13-A31F-3C5955771480}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="165">
   <si>
     <t>V_LNSCHD_AVY    —    Data Lineage Summary</t>
   </si>
@@ -82,7 +82,9 @@
 sat_md_deal_value, sat_loans_payment_due_information, sat_loans_payment_due_overdue
 sat_limit_information, sat_next_payment_amount, link_loans_payment_due
 link_loans_limit, sts_hub_loans, sts_hub_loans_ld_schedule_define
-sts_hub_md_deal, sts_hub_loans_payment_due</t>
+sts_hub_md_deal, sts_hub_loans_payment_due, sts_hub_limit
+hub_consumer_loan
+sts_hub_consumer_loan_next_payment_amount</t>
   </si>
   <si>
     <t>Table (tầng Gold - Databricks)</t>
@@ -133,7 +135,7 @@
         CAST(msr_prd_id AS INT) AS data_date_id,
         msr_prd_dt AS data_date
     FROM IDENTIFIER(:cleaned || '.business_vault.calendar')
-    WHERE msr_prd_dt BETWEEN DATE '2026-01-01' AND TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE msr_prd_dt BETWEEN DATE '2026-01-01' AND TO_DATE(:target_date, 'yyyyMMdd')
 ),
 hub_loans_by_date AS (
     SELECT
@@ -180,8 +182,7 @@
         ON d.data_date_id = hl.data_date_id AND d.loans_hashkey = hl.loans_hashkey
     WHERE d.loans_hashkey IS NULL
 ),
--- Lấy nhiều cột (7 cột: t_k_date, t_sch_type, t_frequency, t_number, t_cycled_dates, t_amount, t_currency)
--- của cùng 1 dòng mới nhất trong sat_loans_schedule =&gt; dùng QUALIFY ROW_NUMBER theo ngưỡng đã chốt (&gt;=3 cột)
+-- Lấy 7 cột của cùng 1 dòng mới nhất trong sat_loans_schedule =&gt; giữ QUALIFY ROW_NUMBER (&gt;5 cột)
 sat_schedule_latest AS (
     SELECT h.data_date_id, h.data_date, h.loans_hashkey, h.loan_id,
            s.t_k_date, s.t_sch_type, s.t_frequency, s.t_number,
@@ -237,10 +238,12 @@
         e.shd_amount,
         e.schedule_currency,
         seq_num,
+        -- Parse frequency dạng "[so][don_vi]" (vd "3M" = 3 thang, "1Q" = 1 quy).
+        -- Neu khong parse duoc so o dau, mac dinh coi la 1 lan lap (frequency_num = 1)
         COALESCE(
-            TRY_CAST(NULLIF(SUBSTRING(TRIM(e.frequency), 1, LENGTH(TRIM(e.frequency)) - 1), '') AS INT),
-            1
+            TRY_CAST(NULLIF(SUBSTRING(TRIM(e.frequency), 1, LENGTH(TRIM(e.frequency)) - 1), '') AS INT), 1
         ) AS frequency_num,
+        -- Don vi tan suat: D=Ngay, M=Thang, Q=Quy, Y=Nam (ky tu cuoi cua frequency)
         UPPER(RIGHT(TRIM(e.frequency), 1)) AS frequency_name
     FROM schedule_exploded e
     LATERAL VIEW EXPLODE(
@@ -271,15 +274,8 @@
 ),
 sat_schedule AS (
     SELECT
-        data_date_id,
-        data_date,
-        loans_hashkey,
-        loan_id,
-        schedule_seq,
-        seq_num,
-        shd_dt,
-        shd_amount,
-        schedule_currency
+        data_date_id, data_date, loans_hashkey, loan_id, schedule_seq,
+        seq_num, shd_dt, shd_amount, schedule_currency
     FROM schedule_generated
     WHERE shd_dt &gt; data_date
 ),
@@ -287,16 +283,15 @@
     SELECT
         sch.data_date_id,
         sch.loan_id                             AS unq_id_src_stm,
+        sch.loans_hashkey                       AS ar_id,
         sch.schedule_currency,
-        CAST(NULL AS STRING)                    AS ar_nm,  -- sat_loans_schedule has no contract-name column
+        CAST(NULL AS STRING)                    AS ar_nm,
         CAST(sch.shd_dt AS TIMESTAMP)           AS shd_dt,
         CAST(sch.shd_amount AS DECIMAL(20,4))   AS shd_amount
     FROM sat_schedule sch
 ),
 -- ============================================================
 -- NHÁNH MD_DEAL: T24 MD_DEAL (SRC_STM_ID 103900049) - nhánh độc lập
--- (review item 4). K_DATE/AVY_AMT lấy từ T_CHARGE_DATE/T_CHARGE_AMT của
--- chính MD_DEAL, không phải enrichment cho nhánh A.
 -- ============================================================
 hub_md_deal_by_date AS (
     SELECT
@@ -327,41 +322,36 @@
         ON d.data_date_id = h.data_date_id AND d.md_deal_hashkey = h.md_deal_hashkey
     WHERE d.md_deal_hashkey IS NULL
 ),
--- 1 cột (t_currency) =&gt; dùng MAX_BY + GROUP BY theo chuẩn thống nhất toàn batch.
--- struct(source_event_date, load_timestamp, hashdiff) giữ nguyên đúng thứ tự tie-break như ORDER BY ... DESC cũ.
 sat_md_deal_info AS (
     SELECT
         md.data_date,
         md.md_deal_hashkey,
-        max_by(di.t_currency, struct(di.source_event_date, di.load_timestamp, di.hashdiff)) AS t_currency
+        max_by(di.t_currency, struct(di.source_event_date, di.load_timestamp)) AS t_currency
     FROM hub_md_deal_active md
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_md_deal_information') di
         ON di.md_deal_hashkey = md.md_deal_hashkey
        AND di.source_event_date &lt;= md.data_date
     GROUP BY md.data_date, md.md_deal_hashkey
 ),
--- 1 cột (t_alternate_id) =&gt; dùng MAX_BY + GROUP BY theo chuẩn thống nhất toàn batch.
 sat_md_deal_other AS (
     SELECT
         md.data_date,
         md.md_deal_hashkey,
-        max_by(ot.t_alternate_id, struct(ot.source_event_date, ot.load_timestamp, ot.hashdiff)) AS t_alternate_id
+        max_by(ot.t_alternate_id, struct(ot.source_event_date, ot.load_timestamp)) AS t_alternate_id
     FROM hub_md_deal_active md
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_md_deal_other') ot
         ON ot.md_deal_hashkey = md.md_deal_hashkey
        AND ot.source_event_date &lt;= md.data_date
     GROUP BY md.data_date, md.md_deal_hashkey
 ),
--- 2 cột (t_charge_date, t_charge_amt) =&gt; dùng MAX_BY + GROUP BY. Dùng CÙNG một struct order
--- cho cả 2 max_by để đảm bảo 2 cột luôn lấy từ đúng 1 dòng "thắng" duy nhất (không lệch dòng).
 sat_md_deal_value_latest AS (
     SELECT
         md.data_date_id,
         md.data_date,
         md.loan_id,
         md.md_deal_hashkey,
-        max_by(v.t_charge_date, struct(v.source_event_date, v.load_timestamp, v.hashdiff)) AS t_charge_date,
-        max_by(v.t_charge_amt, struct(v.source_event_date, v.load_timestamp, v.hashdiff)) AS t_charge_amt
+        max_by(v.t_charge_date, struct(v.source_event_date, v.load_timestamp)) AS t_charge_date,
+        max_by(v.t_charge_amt, struct(v.source_event_date, v.load_timestamp)) AS t_charge_amt
     FROM hub_md_deal_active md
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_md_deal_value') v
         ON v.md_deal_hashkey = md.md_deal_hashkey
@@ -384,6 +374,7 @@
     SELECT
         e.data_date_id,
         e.loan_id                               AS unq_id_src_stm,
+        e.md_deal_hashkey                       AS ar_id,
         di.t_currency                           AS schedule_currency,
         ot.t_alternate_id                       AS ar_nm,
         CAST(e.shd_dt AS TIMESTAMP)             AS shd_dt,
@@ -398,35 +389,47 @@
 cte_snap_sts_hub_loans_payment_due AS (
     SELECT loans_payment_due_hashkey, cdc_status, source_event_date
     FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_loans_payment_due')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
 ),
 cte_snap_sat_loans_payment_due_information AS (
     SELECT loans_payment_due_hashkey, t_currency, t_payment_dte_due,
            source_event_date, load_timestamp, hashdiff
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_loans_payment_due_information')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
 ),
 cte_snap_sat_loans_payment_due_overdue AS (
     SELECT loans_payment_due_hashkey, t_pay_type, t_pay_amt_outs,
            source_event_date, load_timestamp, hashdiff
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_loans_payment_due_overdue')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
 ),
 -- ============================================================
 -- NHÁNH B: T24 Payment Due (SRC_STM_ID 103900006)
 -- ============================================================
-payment_due_link_by_date AS (
+link_loans_payment_due_cur_by_date AS (
     SELECT
         hl.data_date_id,
         hl.data_date,
         hl.loans_hashkey,
-        hl.loan_id,
-        l.loans_payment_due_hashkey
+        l.link_loans_payment_due_hashkey,
+        max_by(l.loans_payment_due_hashkey, l.source_event_date) AS loans_payment_due_hashkey
     FROM hub_loans_active hl
     INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.link_loans_payment_due') l
         ON l.loans_hashkey = hl.loans_hashkey
        AND l.source_event_date &lt;= hl.data_date
-    GROUP BY hl.data_date_id, hl.data_date, hl.loans_hashkey, hl.loan_id, l.loans_payment_due_hashkey
+    GROUP BY hl.data_date_id, hl.data_date, hl.loans_hashkey, l.link_loans_payment_due_hashkey
+),
+payment_due_link_by_date AS (
+    SELECT
+        lnk.data_date_id,
+        lnk.data_date,
+        lnk.loans_hashkey,
+        hl.loan_id,
+        lnk.loans_payment_due_hashkey
+    FROM link_loans_payment_due_cur_by_date lnk
+    INNER JOIN hub_loans_active hl
+        ON hl.data_date_id = lnk.data_date_id
+       AND hl.loans_hashkey = lnk.loans_hashkey
 ),
 payment_due_sts_del_by_date AS (
     SELECT p.data_date_id, p.loans_payment_due_hashkey
@@ -444,14 +447,17 @@
         ON d.data_date_id = p.data_date_id AND d.loans_payment_due_hashkey = p.loans_payment_due_hashkey
     WHERE d.loans_payment_due_hashkey IS NULL
 ),
+-- FIX 2.2: 4 cột (&lt;=5) =&gt; đổi QUALIFY ROW_NUMBER sang MAX_BY, GROUP BY theo khóa
 payment_due_latest AS (
     SELECT
-        p.data_date_id, p.data_date, p.loan_id,
+        p.data_date_id,
+        p.data_date,
+        p.loan_id,
         p.loans_payment_due_hashkey,
-        max_by(info.t_currency, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_currency,
-        max_by(info.t_payment_dte_due, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_payment_dte_due,
-        max_by(od.t_pay_type, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_pay_type,
-        max_by(od.t_pay_amt_outs, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_pay_amt_outs
+        max_by(info.t_currency, struct(info.source_event_date, info.load_timestamp))       AS t_currency,
+        max_by(info.t_payment_dte_due, struct(info.source_event_date, info.load_timestamp)) AS t_payment_dte_due,
+        max_by(od.t_pay_type, struct(od.source_event_date, od.load_timestamp))               AS t_pay_type,
+        max_by(od.t_pay_amt_outs, struct(od.source_event_date, od.load_timestamp))           AS t_pay_amt_outs
     FROM payment_due_active p
     LEFT JOIN cte_snap_sat_loans_payment_due_information info
         ON info.loans_payment_due_hashkey = p.loans_payment_due_hashkey
@@ -485,6 +491,7 @@
     SELECT
         data_date_id,
         loan_id AS unq_id_src_stm,
+        loans_payment_due_hashkey AS ar_id,
         t_currency AS schedule_currency,
         CAST(NULL AS STRING) AS ar_nm,
         CAST(TRY_TO_DATE(due_date_item, 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
@@ -497,7 +504,7 @@
       AND TRY_TO_DATE(due_date_item, 'yyyyMMdd') &gt; data_date
 ),
 -- ============================================================
--- NHÁNH PDPD: T24 Payment Due - thau chi qua han (SRC_STM_ID 103900006,
+-- NHÁNH PDPD: T24 Payment Due - thấu chi quá hạn (SRC_STM_ID 103900006)
 -- ============================================================
 pdpd_hub_by_date AS (
     SELECT
@@ -526,15 +533,17 @@
         ON d.data_date_id = p.data_date_id AND d.loans_payment_due_hashkey = p.loans_payment_due_hashkey
     WHERE d.loans_payment_due_hashkey IS NULL
 ),
--- 4 cột (t_currency, t_payment_dte_due, t_pay_type, t_pay_amt_outs) từ 2 satellite (information + overdue)
--- =&gt; dùng MAX_BY + GROUP BY, cùng struct order như payment_due_latest để giữ đúng tie-break gốc.
+-- FIX 2.2: 4 cột (&lt;=5) =&gt; đổi QUALIFY ROW_NUMBER sang MAX_BY, GROUP BY theo khóa
 pdpd_latest AS (
     SELECT
-        p.data_date_id, p.data_date, p.pdpd_id, p.loans_payment_due_hashkey,
-        max_by(info.t_currency, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_currency,
-        max_by(info.t_payment_dte_due, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_payment_dte_due,
-        max_by(od.t_pay_type, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_pay_type,
-        max_by(od.t_pay_amt_outs, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_pay_amt_outs
+        p.data_date_id,
+        p.data_date,
+        p.pdpd_id,
+        p.loans_payment_due_hashkey,
+        max_by(info.t_currency, struct(info.source_event_date, info.load_timestamp))       AS t_currency,
+        max_by(info.t_payment_dte_due, struct(info.source_event_date, info.load_timestamp)) AS t_payment_dte_due,
+        max_by(od.t_pay_type, struct(od.source_event_date, od.load_timestamp))               AS t_pay_type,
+        max_by(od.t_pay_amt_outs, struct(od.source_event_date, od.load_timestamp))           AS t_pay_amt_outs
     FROM pdpd_active p
     LEFT JOIN cte_snap_sat_loans_payment_due_information info
         ON info.loans_payment_due_hashkey = p.loans_payment_due_hashkey
@@ -544,7 +553,6 @@
        AND od.source_event_date &lt;= p.data_date
     GROUP BY p.data_date_id, p.data_date, p.pdpd_id, p.loans_payment_due_hashkey
 ),
--- Fix: cung delimiter 2 tang '::'+'!!' nhu branch_payment_due (xem comment o do).
 pdpd_installments AS (
     SELECT
         p.data_date_id, p.data_date, p.pdpd_id, p.loans_payment_due_hashkey, p.t_currency,
@@ -569,6 +577,7 @@
     SELECT
         data_date_id,
         pdpd_id AS unq_id_src_stm,
+        loans_payment_due_hashkey AS ar_id,
         t_currency AS schedule_currency,
         CAST(NULL AS STRING) AS ar_nm,
         CAST(TRY_TO_DATE(due_date_item, 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
@@ -585,83 +594,148 @@
 -- ============================================================
 link_loans_limit_cur_by_date AS (
     SELECT
-        hl.data_date_id,
-        hl.data_date,
-        hl.loans_hashkey,
-        ll.limit_hashkey
+        hl.data_date_id, hl.data_date, hl.loans_hashkey,
+        max_by(ll.limit_hashkey, ll.source_event_date) AS limit_hashkey
     FROM hub_loans_active hl
-    INNER  JOIN IDENTIFIER(:cleaned || '.raw_vault.link_loans_limit') ll
+    INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.link_loans_limit') ll
         ON ll.loans_hashkey = hl.loans_hashkey
        AND ll.source_event_date &lt;= hl.data_date
-    GROUP BY hl.data_date_id, hl.data_date, hl.loans_hashkey, ll.limit_hashkey
+    GROUP BY hl.data_date_id, hl.data_date, hl.loans_hashkey
+),
+limit_sts_del_by_date AS (
+    SELECT ll.data_date_id, ll.limit_hashkey
+    FROM link_loans_limit_cur_by_date ll
+    JOIN IDENTIFIER(:cleaned || '.raw_vault.sts_hub_limit') sts
+        ON sts.limit_hashkey = ll.limit_hashkey
+       AND sts.source_event_date &lt;= ll.data_date
+    GROUP BY ll.data_date_id, ll.limit_hashkey
+    HAVING max_by(sts.cdc_status, sts.source_event_date) = 'D'
 ),
 limit_active AS (
     SELECT ll.data_date_id, ll.data_date, lim.business_key AS unq_id_src_stm, lim.limit_hashkey
     FROM link_loans_limit_cur_by_date ll
     INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_limit') lim
         ON lim.limit_hashkey = ll.limit_hashkey
-),
--- 2 cột (t_limit_currency, t_expiry_date) =&gt; dùng MAX_BY + GROUP BY. WHERE lọc theo t_expiry_date
-branch_limit AS (
+    LEFT JOIN limit_sts_del_by_date d
+        ON d.data_date_id = ll.data_date_id AND d.limit_hashkey = ll.limit_hashkey
+    WHERE d.limit_hashkey IS NULL
+),
+-- FIX 2.2: 2 cột (&lt;=5) =&gt; đổi QUALIFY ROW_NUMBER sang MAX_BY, GROUP BY theo khóa
+sat_limit_latest AS (
     SELECT
         l.data_date_id,
+        l.data_date,
         l.unq_id_src_stm,
-        max_by(info.t_limit_currency, struct(info.source_event_date, info.load_timestamp, info.hashdiff)) AS schedule_currency,
-        CAST(NULL AS STRING)    AS ar_nm,
-        CAST(TRY_TO_DATE(max_by(info.t_expiry_date, struct(info.source_event_date, info.load_timestamp, info.hashdiff)), 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
-        CAST(NULL AS DECIMAL(20,4)) AS shd_amount
+        l.limit_hashkey,
+        max_by(info.t_limit_currency, struct(info.source_event_date, info.load_timestamp)) AS t_limit_currency,
+        max_by(info.t_expiry_date, struct(info.source_event_date, info.load_timestamp))    AS t_expiry_date
     FROM limit_active l
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_limit_information') info
         ON info.limit_hashkey = l.limit_hashkey
        AND info.source_event_date &lt;= l.data_date
-    WHERE TRY_TO_DATE(info.t_expiry_date, 'yyyyMMdd') &gt; l.data_date
     GROUP BY l.data_date_id, l.data_date, l.unq_id_src_stm, l.limit_hashkey
+),
+branch_limit AS (
+    SELECT
+        data_date_id,
+        unq_id_src_stm,
+        limit_hashkey AS ar_id,
+        t_limit_currency AS schedule_currency,
+        CAST(NULL AS STRING) AS ar_nm,
+        CAST(TRY_TO_DATE(t_expiry_date, 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
+        CAST(NULL AS DECIMAL(20,4)) AS shd_amount
+    FROM sat_limit_latest
+    WHERE TRY_TO_DATE(t_expiry_date, 'yyyyMMdd') &gt; data_date
 ),
 -- ============================================================
 -- NHÁNH D: COMB Next Payment Amount (SRC_STM_ID 103900067)
+-- ============================================================
+hub_consumer_loan_by_date AS (
+    SELECT
+        c.data_date_id,
+        c.data_date,
+        h.consumer_loan_hashkey,
+        h.business_key AS contractcode
+    FROM calendar_dates c
+    INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_consumer_loan') h
+        ON h.source_event_date &lt;= c.data_date
+),
+next_payment_sts_del_by_date AS (
+    SELECT hc.data_date_id, hc.consumer_loan_hashkey
+    FROM hub_consumer_loan_by_date hc
+    JOIN IDENTIFIER(:cleaned || '.raw_vault.sts_hub_consumer_loan_next_payment_amount') sts
+        ON sts.consumer_loan_hashkey = hc.consumer_loan_hashkey
+       AND sts.source_event_date &lt;= hc.data_date
+    GROUP BY hc.data_date_id, hc.consumer_loan_hashkey
+    HAVING max_by(sts.cdc_status, sts.source_event_date) = 'D'
+),
+hub_consumer_loan_active AS (
+    SELECT hc.data_date_id, hc.data_date, hc.consumer_loan_hashkey, hc.contractcode
+    FROM hub_consumer_loan_by_date hc
+    LEFT JOIN next_payment_sts_del_by_date d
+        ON d.data_date_id = hc.data_date_id
+        AND d.consumer_loan_hashkey = hc.consumer_loan_hashkey
+    WHERE d.consumer_loan_hashkey IS NULL
+),
+-- FIX 2.2: 3 cột (&lt;=5) =&gt; đổi QUALIFY ROW_NUMBER sang MAX_BY, GROUP BY theo khóa (giữ ma_key trong GROUP BY như logic gốc)
+sat_next_payment_latest AS (
+    SELECT
+        hc.data_date_id,
+        hc.data_date,
+        hc.consumer_loan_hashkey,
+        hc.contractcode,
+        s.ma_key,
+        max_by(s.duedate, struct(s.source_event_date, s.load_timestamp))         AS duedate,
+        max_by(s.principal, struct(s.source_event_date, s.load_timestamp))       AS principal,
+        max_by(s.remainprincipal, struct(s.source_event_date, s.load_timestamp)) AS remainprincipal
+    FROM hub_consumer_loan_active hc
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_next_payment_amount') s
+        ON s.consumer_loan_hashkey = hc.consumer_loan_hashkey
+       AND s.source_event_date &lt;= hc.data_date
+    GROUP BY hc.data_date_id, hc.data_date, hc.consumer_loan_hashkey, hc.contractcode, s.ma_key
+),
 branch_comb_next_payment AS (
     SELECT
-        c.data_date_id,
-        max_by(s.contractcode, struct(s.source_event_date, s.load_timestamp, s.hashdiff)) AS unq_id_src_stm,
-        CAST(NULL AS STRING)     AS schedule_currency,  -- sat_next_payment_amount không có cột currency
-        CAST(NULL AS STRING)     AS ar_nm,
-        CAST(TRY_TO_DATE(max_by(s.duedate, struct(s.source_event_date, s.load_timestamp, s.hashdiff)), 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
-        CAST(max_by(s.principal, struct(s.source_event_date, s.load_timestamp, s.hashdiff)) AS DECIMAL(20,4)) AS shd_amount
-    FROM calendar_dates c
-    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_next_payment_amount') s
-        ON s.source_event_date &lt;= c.data_date
-    WHERE TRY_TO_DATE(s.duedate, 'yyyyMMdd') &gt; c.data_date
-      AND NVL(TRY_CAST(s.remainprincipal AS DECIMAL(20,4)), CAST(0 AS DECIMAL(20,4))) &lt;&gt; 0
-    GROUP BY c.data_date_id, c.data_date, s.next_payment_amount_hashkey
+        data_date_id,
+        contractcode AS unq_id_src_stm,
+        consumer_loan_hashkey AS ar_id,
+        CAST(NULL AS STRING) AS schedule_currency,
+        CAST(NULL AS STRING) AS ar_nm,
+        CAST(TRY_TO_DATE(duedate, 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
+        CAST(principal AS DECIMAL(20,4)) AS shd_amount
+    FROM sat_next_payment_latest
+    WHERE TRY_TO_DATE(duedate, 'yyyyMMdd') &gt; data_date
+      AND NVL(TRY_CAST(remainprincipal AS DECIMAL(20,4)), CAST(0 AS DECIMAL(20,4))) &lt;&gt; 0
 ),
 unioned_raw AS (
-    SELECT 'LD_SCHEDULE' AS source_branch, data_date_id, unq_id_src_stm, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_ld_schedule
+    SELECT 'LD_SCHEDULE' AS source_branch, data_date_id, unq_id_src_stm, ar_id, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_ld_schedule
     UNION ALL
-    SELECT 'MD_DEAL', data_date_id, unq_id_src_stm, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_md_deal
+    SELECT 'MD_DEAL', data_date_id, unq_id_src_stm, ar_id, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_md_deal
     UNION ALL
-    SELECT 'PAYMENT_DUE', data_date_id, unq_id_src_stm, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_payment_due
+    SELECT 'PAYMENT_DUE', data_date_id, unq_id_src_stm, ar_id, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_payment_due
     UNION ALL
-    SELECT 'PDPD', data_date_id, unq_id_src_stm, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_pdpd
+    SELECT 'PDPD', data_date_id, unq_id_src_stm, ar_id, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_pdpd
     UNION ALL
-    SELECT 'LIMIT', data_date_id, unq_id_src_stm, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_limit
+    SELECT 'LIMIT', data_date_id, unq_id_src_stm, ar_id, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_limit
     UNION ALL
-    SELECT 'COMB_NEXT_PAYMENT', data_date_id, unq_id_src_stm, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_comb_next_payment
+    SELECT 'COMB_NEXT_PAYMENT', data_date_id, unq_id_src_stm, ar_id, schedule_currency, ar_nm, shd_dt, shd_amount FROM branch_comb_next_payment
 ),
 unioned AS (
     SELECT
         source_branch,
         data_date_id,
         unq_id_src_stm,
+        ar_id,
         schedule_currency,
         ar_nm,
         shd_dt,
-        SUM(shd_amount) AS shd_amount
+        NVL(SUM(shd_amount), 0) AS shd_amount
     FROM unioned_raw
-    GROUP BY source_branch, data_date_id, unq_id_src_stm, schedule_currency, ar_nm, shd_dt
+    GROUP BY source_branch, data_date_id, unq_id_src_stm, ar_id, schedule_currency, ar_nm, shd_dt
 )
 SELECT
     data_date_id                AS CDR_DT_ID,
-    CAST(NULL AS BIGINT)         AS AR_ID,    
+    ar_id                        AS AR_ID,
     101500001                    AS AVY_TP_ID,
     schedule_currency            AS DNMN_CCY_ID,
     unq_id_src_stm                AS UNQ_ID_SRC_STM,
@@ -692,7 +766,7 @@
     <t>calendar_dates AS (
     SELECT CAST(msr_prd_id AS INT) AS data_date_id, msr_prd_dt AS data_date
     FROM IDENTIFIER(:cleaned || '.business_vault.calendar')
-    WHERE msr_prd_dt BETWEEN DATE '2026-01-01' AND TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE msr_prd_dt BETWEEN DATE '2026-01-01' AND TO_DATE(:target_date, 'yyyyMMdd')
 )</t>
   </si>
   <si>
@@ -801,7 +875,7 @@
     <t>s</t>
   </si>
   <si>
-    <t>s.loans_hashkey = h.loans_hashkey AND s.source_event_date &lt;= h.data_date</t>
+    <t>s.loans_hashkey = h.loans_hashkey AND s.source_event_date &lt;= h.data_date (giu QUALIFY ROW_NUMBER, 7 cot &gt;5)</t>
   </si>
   <si>
     <t>schedule_exploded AS (
@@ -825,6 +899,9 @@
     <t>e</t>
   </si>
   <si>
+    <t>LATERAL VIEW POSEXPLODE, khong co join</t>
+  </si>
+  <si>
     <t>schedule_recurrence AS (
     SELECT e.data_date_id, e.data_date, e.loans_hashkey, e.loan_id, e.schedule_seq,
            e.start_dt, e.sch_type, e.frequency, e.number_of_periods,
@@ -839,6 +916,9 @@
   </si>
   <si>
     <t>q</t>
+  </si>
+  <si>
+    <t>LATERAL VIEW EXPLODE(SEQUENCE), khong co join</t>
   </si>
   <si>
     <t>schedule_generated AS (
@@ -858,6 +938,9 @@
 )</t>
   </si>
   <si>
+    <t>Filter only, khong co join</t>
+  </si>
+  <si>
     <t>sat_schedule AS (
     SELECT data_date_id, data_date, loans_hashkey, loan_id, schedule_seq, seq_num,
            shd_dt, shd_amount, schedule_currency
@@ -869,12 +952,19 @@
     <t>sch</t>
   </si>
   <si>
+    <t>Filter shd_dt &gt; data_date, khong co join</t>
+  </si>
+  <si>
     <t>branch_ld_schedule AS (
-    SELECT sch.data_date_id, sch.loan_id AS unq_id_src_stm, sch.schedule_currency,
-           CAST(NULL AS STRING) AS ar_nm, CAST(sch.shd_dt AS TIMESTAMP) AS shd_dt,
+    SELECT sch.data_date_id, sch.loan_id AS unq_id_src_stm, sch.loans_hashkey AS ar_id,
+           sch.schedule_currency, CAST(NULL AS STRING) AS ar_nm,
+           CAST(sch.shd_dt AS TIMESTAMP) AS shd_dt,
            CAST(sch.shd_amount AS DECIMAL(20,4)) AS shd_amount
     FROM sat_schedule sch
 )</t>
+  </si>
+  <si>
+    <t>AR_ID = loans_hashkey</t>
   </si>
   <si>
     <t>hub_md_deal_by_date AS (
@@ -890,9 +980,6 @@
   </si>
   <si>
     <t>md.business_key = hl.loan_id AND md.source_event_date &lt;= hl.data_date</t>
-  </si>
-  <si>
-    <t>14a</t>
   </si>
   <si>
     <t>md_deal_sts_del_by_date AS (
@@ -908,9 +995,6 @@
     <t>sts.md_deal_hashkey = h.md_deal_hashkey AND sts.source_event_date &lt;= h.data_date</t>
   </si>
   <si>
-    <t>14b</t>
-  </si>
-  <si>
     <t>hub_md_deal_active AS (
     SELECT h.data_date_id, h.data_date, h.loans_hashkey, h.loan_id, h.md_deal_hashkey, h.md_deal_id
     FROM hub_md_deal_by_date h
@@ -925,7 +1009,7 @@
   <si>
     <t>sat_md_deal_info AS (
     SELECT md.data_date, md.md_deal_hashkey,
-        max_by(di.t_currency, struct(di.source_event_date, di.load_timestamp, di.hashdiff)) AS t_currency
+        max_by(di.t_currency, struct(di.source_event_date, di.load_timestamp)) AS t_currency
     FROM hub_md_deal_active md
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_md_deal_information') di
         ON di.md_deal_hashkey = md.md_deal_hashkey AND di.source_event_date &lt;= md.data_date
@@ -941,7 +1025,7 @@
   <si>
     <t>sat_md_deal_other AS (
     SELECT md.data_date, md.md_deal_hashkey,
-        max_by(ot.t_alternate_id, struct(ot.source_event_date, ot.load_timestamp, ot.hashdiff)) AS t_alternate_id
+        max_by(ot.t_alternate_id, struct(ot.source_event_date, ot.load_timestamp)) AS t_alternate_id
     FROM hub_md_deal_active md
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_md_deal_other') ot
         ON ot.md_deal_hashkey = md.md_deal_hashkey AND ot.source_event_date &lt;= md.data_date
@@ -957,8 +1041,8 @@
   <si>
     <t>sat_md_deal_value_latest AS (
     SELECT md.data_date_id, md.data_date, md.loan_id, md.md_deal_hashkey,
-        max_by(v.t_charge_date, struct(v.source_event_date, v.load_timestamp, v.hashdiff)) AS t_charge_date,
-        max_by(v.t_charge_amt, struct(v.source_event_date, v.load_timestamp, v.hashdiff)) AS t_charge_amt
+        max_by(v.t_charge_date, struct(v.source_event_date, v.load_timestamp)) AS t_charge_date,
+        max_by(v.t_charge_amt, struct(v.source_event_date, v.load_timestamp)) AS t_charge_amt
     FROM hub_md_deal_active md
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_md_deal_value') v
         ON v.md_deal_hashkey = md.md_deal_hashkey AND v.source_event_date &lt;= md.data_date
@@ -982,8 +1066,9 @@
   </si>
   <si>
     <t>branch_md_deal AS (
-    SELECT e.data_date_id, e.loan_id AS unq_id_src_stm, di.t_currency AS schedule_currency,
-           ot.t_alternate_id AS ar_nm, CAST(e.shd_dt AS TIMESTAMP) AS shd_dt,
+    SELECT e.data_date_id, e.loan_id AS unq_id_src_stm, e.md_deal_hashkey AS ar_id,
+           di.t_currency AS schedule_currency, ot.t_alternate_id AS ar_nm,
+           CAST(e.shd_dt AS TIMESTAMP) AS shd_dt,
            CAST(e.shd_amount AS DECIMAL(20,4)) AS shd_amount
     FROM md_deal_exploded e
     LEFT JOIN sat_md_deal_info di ON di.data_date = e.data_date AND di.md_deal_hashkey = e.md_deal_hashkey
@@ -992,47 +1077,43 @@
 )</t>
   </si>
   <si>
-    <t>di: di.data_date = e.data_date AND di.md_deal_hashkey = e.md_deal_hashkey | ot: ot.data_date = e.data_date AND ot.md_deal_hashkey = e.md_deal_hashkey</t>
-  </si>
-  <si>
-    <t>cte_snap_sts_hub_loans_payment_due, cte_snap_sat_loans_payment_due_information,
+    <t>di: di.data_date = e.data_date AND di.md_deal_hashkey = e.md_deal_hashkey | ot: ot.data_date = e.data_date AND ot.md_deal_hashkey = e.md_deal_hashkey. AR_ID = md_deal_hashkey</t>
+  </si>
+  <si>
+    <t>cte_snap_sts_hub_loans_payment_due,
+cte_snap_sat_loans_payment_due_information,
 cte_snap_sat_loans_payment_due_overdue
-(WHERE source_event_date &lt;= :DATADT)</t>
-  </si>
-  <si>
-    <t>21a</t>
-  </si>
-  <si>
-    <t>link_loans_payment_due_current_by_date AS (
-    SELECT c.data_date_id, c.data_date, l.loans_hashkey, l.loans_payment_due_hashkey
-    FROM calendar_dates c
+(snapshot CTE, WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd'))</t>
+  </si>
+  <si>
+    <t>Snapshot 1 lan doc Silver, tai su dung cho ca PAYMENT_DUE va PDPD (rule 2.12)</t>
+  </si>
+  <si>
+    <t>link_loans_payment_due_cur_by_date AS (
+    SELECT hl.data_date_id, hl.data_date, hl.loans_hashkey, l.link_loans_payment_due_hashkey,
+        max_by(l.loans_payment_due_hashkey, l.source_event_date) AS loans_payment_due_hashkey
+    FROM hub_loans_active hl
     INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.link_loans_payment_due') l
-        ON l.source_event_date &lt;= c.data_date
-    GROUP BY c.data_date_id, c.data_date, l.loans_hashkey, l.loans_payment_due_hashkey
+        ON l.loans_hashkey = hl.loans_hashkey AND l.source_event_date &lt;= hl.data_date
+    GROUP BY hl.data_date_id, hl.data_date, hl.loans_hashkey, l.link_loans_payment_due_hashkey
 )</t>
   </si>
   <si>
     <t>l</t>
   </si>
   <si>
-    <t>l.source_event_date &lt;= c.data_date</t>
-  </si>
-  <si>
-    <t>21b</t>
+    <t>l.loans_hashkey = hl.loans_hashkey AND l.source_event_date &lt;= hl.data_date (dedup link bang MAX_BY, 1 cot)</t>
   </si>
   <si>
     <t>payment_due_link_by_date AS (
-    SELECT hl.data_date_id, hl.data_date, hl.loans_hashkey, hl.loan_id, l.loans_payment_due_hashkey
-    FROM hub_loans_active hl
-    INNER JOIN link_loans_payment_due_current_by_date l
-        ON l.data_date_id = hl.data_date_id AND l.loans_hashkey = hl.loans_hashkey
-)</t>
-  </si>
-  <si>
-    <t>l.data_date_id = hl.data_date_id AND l.loans_hashkey = hl.loans_hashkey</t>
-  </si>
-  <si>
-    <t>22a</t>
+    SELECT lnk.data_date_id, lnk.data_date, lnk.loans_hashkey, hl.loan_id, lnk.loans_payment_due_hashkey
+    FROM link_loans_payment_due_cur_by_date lnk
+    INNER JOIN hub_loans_active hl
+        ON hl.data_date_id = lnk.data_date_id AND hl.loans_hashkey = lnk.loans_hashkey
+)</t>
+  </si>
+  <si>
+    <t>hl.data_date_id = lnk.data_date_id AND hl.loans_hashkey = lnk.loans_hashkey</t>
   </si>
   <si>
     <t>payment_due_sts_del_by_date AS (
@@ -1049,9 +1130,6 @@
     <t>sts.loans_payment_due_hashkey = p.loans_payment_due_hashkey AND sts.source_event_date &lt;= p.data_date</t>
   </si>
   <si>
-    <t>22b</t>
-  </si>
-  <si>
     <t>payment_due_active AS (
     SELECT p.data_date_id, p.data_date, p.loans_hashkey, p.loan_id, p.loans_payment_due_hashkey
     FROM payment_due_link_by_date p
@@ -1065,20 +1143,17 @@
   </si>
   <si>
     <t>payment_due_latest AS (
-    SELECT
-        p.data_date_id, p.data_date, p.loan_id,
-        p.loans_payment_due_hashkey,
-        max_by(info.t_currency, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_currency,
-        max_by(info.t_payment_dte_due, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_payment_dte_due,
-        max_by(od.t_pay_type, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_pay_type,
-        max_by(od.t_pay_amt_outs, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_pay_amt_outs
+    -- FIX 2.2: 4 cot (&lt;=5) =&gt; MAX_BY thay QUALIFY ROW_NUMBER, GROUP BY theo khoa
+    SELECT p.data_date_id, p.data_date, p.loan_id, p.loans_payment_due_hashkey,
+        max_by(info.t_currency, struct(info.source_event_date, info.load_timestamp)) AS t_currency,
+        max_by(info.t_payment_dte_due, struct(info.source_event_date, info.load_timestamp)) AS t_payment_dte_due,
+        max_by(od.t_pay_type, struct(od.source_event_date, od.load_timestamp)) AS t_pay_type,
+        max_by(od.t_pay_amt_outs, struct(od.source_event_date, od.load_timestamp)) AS t_pay_amt_outs
     FROM payment_due_active p
     LEFT JOIN cte_snap_sat_loans_payment_due_information info
-        ON info.loans_payment_due_hashkey = p.loans_payment_due_hashkey
-       AND info.source_event_date &lt;= p.data_date
+        ON info.loans_payment_due_hashkey = p.loans_payment_due_hashkey AND info.source_event_date &lt;= p.data_date
     LEFT JOIN cte_snap_sat_loans_payment_due_overdue od
-        ON od.loans_payment_due_hashkey = p.loans_payment_due_hashkey
-       AND od.source_event_date &lt;= p.data_date
+        ON od.loans_payment_due_hashkey = p.loans_payment_due_hashkey AND od.source_event_date &lt;= p.data_date
     GROUP BY p.data_date_id, p.data_date, p.loan_id, p.loans_payment_due_hashkey
 )</t>
   </si>
@@ -1089,52 +1164,36 @@
     <t>info: info.loans_payment_due_hashkey = p.loans_payment_due_hashkey AND info.source_event_date &lt;= p.data_date | od: od.loans_payment_due_hashkey = p.loans_payment_due_hashkey AND od.source_event_date &lt;= p.data_date</t>
   </si>
   <si>
-    <t>24a</t>
-  </si>
-  <si>
     <t>payment_due_installments AS (
-    SELECT
-        p.data_date_id, p.data_date, p.loan_id, p.loans_payment_due_hashkey, p.t_currency,
+    SELECT p.data_date_id, p.data_date, p.loan_id, p.loans_payment_due_hashkey, p.t_currency,
         outer_pos,
-        CASE
-            WHEN SIZE(SPLIT(REGEXP_REPLACE(p.t_payment_dte_due, '::+', '::'), '::')) = 1
-                THEN p.t_payment_dte_due
-            ELSE ELEMENT_AT(SPLIT(REGEXP_REPLACE(p.t_payment_dte_due, '::+', '::'), '::'), outer_pos + 1)
-        END AS due_date_item,
+        CASE WHEN SIZE(SPLIT(REGEXP_REPLACE(p.t_payment_dte_due, '::+', '::'), '::')) = 1
+             THEN p.t_payment_dte_due
+             ELSE ELEMENT_AT(SPLIT(REGEXP_REPLACE(p.t_payment_dte_due, '::+', '::'), '::'), outer_pos + 1) END AS due_date_item,
         pay_type_group,
-        CASE
-            WHEN SIZE(SPLIT(REGEXP_REPLACE(p.t_pay_amt_outs, '::+', '::'), '::')) = 1
-                THEN p.t_pay_amt_outs
-            ELSE ELEMENT_AT(SPLIT(REGEXP_REPLACE(p.t_pay_amt_outs, '::+', '::'), '::'), outer_pos + 1)
-        END AS amt_group
+        CASE WHEN SIZE(SPLIT(REGEXP_REPLACE(p.t_pay_amt_outs, '::+', '::'), '::')) = 1
+             THEN p.t_pay_amt_outs
+             ELSE ELEMENT_AT(SPLIT(REGEXP_REPLACE(p.t_pay_amt_outs, '::+', '::'), '::'), outer_pos + 1) END AS amt_group
     FROM payment_due_latest p
-    LATERAL VIEW POSEXPLODE(
-        SPLIT(REGEXP_REPLACE(p.t_pay_type, '::+', '::'), '::')
-    ) x AS outer_pos, pay_type_group
+    LATERAL VIEW POSEXPLODE(SPLIT(REGEXP_REPLACE(p.t_pay_type, '::+', '::'), '::')) x AS outer_pos, pay_type_group
 )</t>
   </si>
   <si>
     <t>x</t>
   </si>
   <si>
-    <t>24b</t>
-  </si>
-  <si>
     <t>branch_payment_due AS (
-    SELECT
-        data_date_id,
-        loan_id AS unq_id_src_stm,
-        t_currency AS schedule_currency,
-        CAST(NULL AS STRING) AS ar_nm,
+    SELECT data_date_id, loan_id AS unq_id_src_stm, loans_payment_due_hashkey AS ar_id,
+        t_currency AS schedule_currency, CAST(NULL AS STRING) AS ar_nm,
         CAST(TRY_TO_DATE(due_date_item, 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
-        TRY_CAST(
-            ELEMENT_AT(SPLIT(amt_group, '!!'), ARRAY_POSITION(SPLIT(UPPER(TRIM(pay_type_group)), '!!'), 'PR'))
-            AS DECIMAL(20,4)
-        ) AS shd_amount
+        TRY_CAST(ELEMENT_AT(SPLIT(amt_group, '!!'), ARRAY_POSITION(SPLIT(UPPER(TRIM(pay_type_group)), '!!'), 'PR')) AS DECIMAL(20,4)) AS shd_amount
     FROM payment_due_installments
     WHERE ARRAY_POSITION(SPLIT(UPPER(TRIM(pay_type_group)), '!!'), 'PR') &gt; 0
       AND TRY_TO_DATE(due_date_item, 'yyyyMMdd') &gt; data_date
 )</t>
+  </si>
+  <si>
+    <t>AR_ID = loans_payment_due_hashkey. Chi lay pay_type = 'PR' va due_date &gt; data_date</t>
   </si>
   <si>
     <t>pdpd_hub_by_date AS (
@@ -1148,21 +1207,14 @@
     <t>h.source_event_date &lt;= c.data_date AND h.business_key LIKE 'PDPD%'</t>
   </si>
   <si>
-    <t>26a</t>
-  </si>
-  <si>
     <t>pdpd_sts_del_by_date AS (
     SELECT p.data_date_id, p.loans_payment_due_hashkey
     FROM pdpd_hub_by_date p
     JOIN cte_snap_sts_hub_loans_payment_due sts
-        ON sts.loans_payment_due_hashkey = p.loans_payment_due_hashkey
-       AND sts.source_event_date &lt;= p.data_date
+        ON sts.loans_payment_due_hashkey = p.loans_payment_due_hashkey AND sts.source_event_date &lt;= p.data_date
     GROUP BY p.data_date_id, p.loans_payment_due_hashkey
     HAVING max_by(sts.cdc_status, sts.source_event_date) = 'D'
 )</t>
-  </si>
-  <si>
-    <t>26b</t>
   </si>
   <si>
     <t>pdpd_active AS (
@@ -1174,102 +1226,78 @@
 )</t>
   </si>
   <si>
-    <t>26c</t>
-  </si>
-  <si>
     <t>pdpd_latest AS (
-    SELECT
-        p.data_date_id, p.data_date, p.pdpd_id, p.loans_payment_due_hashkey,
-        max_by(info.t_currency, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_currency,
-        max_by(info.t_payment_dte_due, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_payment_dte_due,
-        max_by(od.t_pay_type, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_pay_type,
-        max_by(od.t_pay_amt_outs, struct(info.source_event_date, od.source_event_date, info.load_timestamp, od.load_timestamp)) AS t_pay_amt_outs
+    -- FIX 2.2: 4 cot (&lt;=5) =&gt; MAX_BY thay QUALIFY ROW_NUMBER, GROUP BY theo khoa
+    SELECT p.data_date_id, p.data_date, p.pdpd_id, p.loans_payment_due_hashkey,
+        max_by(info.t_currency, struct(info.source_event_date, info.load_timestamp)) AS t_currency,
+        max_by(info.t_payment_dte_due, struct(info.source_event_date, info.load_timestamp)) AS t_payment_dte_due,
+        max_by(od.t_pay_type, struct(od.source_event_date, od.load_timestamp)) AS t_pay_type,
+        max_by(od.t_pay_amt_outs, struct(od.source_event_date, od.load_timestamp)) AS t_pay_amt_outs
     FROM pdpd_active p
     LEFT JOIN cte_snap_sat_loans_payment_due_information info
-        ON info.loans_payment_due_hashkey = p.loans_payment_due_hashkey
-       AND info.source_event_date &lt;= p.data_date
+        ON info.loans_payment_due_hashkey = p.loans_payment_due_hashkey AND info.source_event_date &lt;= p.data_date
     LEFT JOIN cte_snap_sat_loans_payment_due_overdue od
-        ON od.loans_payment_due_hashkey = p.loans_payment_due_hashkey
-       AND od.source_event_date &lt;= p.data_date
+        ON od.loans_payment_due_hashkey = p.loans_payment_due_hashkey AND od.source_event_date &lt;= p.data_date
     GROUP BY p.data_date_id, p.data_date, p.pdpd_id, p.loans_payment_due_hashkey
 )</t>
   </si>
   <si>
-    <t>26d</t>
-  </si>
-  <si>
     <t>pdpd_installments AS (
-    SELECT
-        p.data_date_id, p.data_date, p.pdpd_id, p.loans_payment_due_hashkey, p.t_currency,
+    SELECT p.data_date_id, p.data_date, p.pdpd_id, p.loans_payment_due_hashkey, p.t_currency,
         outer_pos,
-        CASE
-            WHEN SIZE(SPLIT(REGEXP_REPLACE(p.t_payment_dte_due, '::+', '::'), '::')) = 1
-                THEN p.t_payment_dte_due
-            ELSE ELEMENT_AT(SPLIT(REGEXP_REPLACE(p.t_payment_dte_due, '::+', '::'), '::'), outer_pos + 1)
-        END AS due_date_item,
+        CASE WHEN SIZE(SPLIT(REGEXP_REPLACE(p.t_payment_dte_due, '::+', '::'), '::')) = 1
+             THEN p.t_payment_dte_due
+             ELSE ELEMENT_AT(SPLIT(REGEXP_REPLACE(p.t_payment_dte_due, '::+', '::'), '::'), outer_pos + 1) END AS due_date_item,
         pay_type_group,
-        CASE
-            WHEN SIZE(SPLIT(REGEXP_REPLACE(p.t_pay_amt_outs, '::+', '::'), '::')) = 1
-                THEN p.t_pay_amt_outs
-            ELSE ELEMENT_AT(SPLIT(REGEXP_REPLACE(p.t_pay_amt_outs, '::+', '::'), '::'), outer_pos + 1)
-        END AS amt_group
+        CASE WHEN SIZE(SPLIT(REGEXP_REPLACE(p.t_pay_amt_outs, '::+', '::'), '::')) = 1
+             THEN p.t_pay_amt_outs
+             ELSE ELEMENT_AT(SPLIT(REGEXP_REPLACE(p.t_pay_amt_outs, '::+', '::'), '::'), outer_pos + 1) END AS amt_group
     FROM pdpd_latest p
-    LATERAL VIEW POSEXPLODE(
-        SPLIT(REGEXP_REPLACE(p.t_pay_type, '::+', '::'), '::')
-    ) x AS outer_pos, pay_type_group
-)</t>
-  </si>
-  <si>
-    <t>26e</t>
+    LATERAL VIEW POSEXPLODE(SPLIT(REGEXP_REPLACE(p.t_pay_type, '::+', '::'), '::')) x AS outer_pos, pay_type_group
+)</t>
   </si>
   <si>
     <t>branch_pdpd AS (
-    SELECT
-        data_date_id,
-        pdpd_id AS unq_id_src_stm,
-        t_currency AS schedule_currency,
-        CAST(NULL AS STRING) AS ar_nm,
+    SELECT data_date_id, pdpd_id AS unq_id_src_stm, loans_payment_due_hashkey AS ar_id,
+        t_currency AS schedule_currency, CAST(NULL AS STRING) AS ar_nm,
         CAST(TRY_TO_DATE(due_date_item, 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
-        TRY_CAST(
-            ELEMENT_AT(SPLIT(amt_group, '!!'), ARRAY_POSITION(SPLIT(UPPER(TRIM(pay_type_group)), '!!'), 'PR'))
-            AS DECIMAL(20,4)
-        ) AS shd_amount
+        TRY_CAST(ELEMENT_AT(SPLIT(amt_group, '!!'), ARRAY_POSITION(SPLIT(UPPER(TRIM(pay_type_group)), '!!'), 'PR')) AS DECIMAL(20,4)) AS shd_amount
     FROM pdpd_installments
     WHERE ARRAY_POSITION(SPLIT(UPPER(TRIM(pay_type_group)), '!!'), 'PR') &gt; 0
       AND TRY_TO_DATE(due_date_item, 'yyyyMMdd') &gt; data_date
 )</t>
   </si>
   <si>
-    <t>27a</t>
-  </si>
-  <si>
-    <t>link_loans_limit_current_by_date AS (
-    SELECT c.data_date_id, c.data_date, ll.loans_hashkey, ll.limit_hashkey
-    FROM calendar_dates c
+    <t>AR_ID = loans_payment_due_hashkey (nhanh PDPD, business_key LIKE 'PDPD%')</t>
+  </si>
+  <si>
+    <t>link_loans_limit_cur_by_date AS (
+    SELECT hl.data_date_id, hl.data_date, hl.loans_hashkey,
+        max_by(ll.limit_hashkey, ll.source_event_date) AS limit_hashkey
+    FROM hub_loans_active hl
     INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.link_loans_limit') ll
-        ON ll.source_event_date &lt;= c.data_date
-    GROUP BY c.data_date_id, c.data_date, ll.loans_hashkey, ll.limit_hashkey
+        ON ll.loans_hashkey = hl.loans_hashkey AND ll.source_event_date &lt;= hl.data_date
+    GROUP BY hl.data_date_id, hl.data_date, hl.loans_hashkey
 )</t>
   </si>
   <si>
     <t>ll</t>
   </si>
   <si>
-    <t>ll.source_event_date &lt;= c.data_date</t>
-  </si>
-  <si>
-    <t>27b</t>
-  </si>
-  <si>
-    <t>link_loans_limit_cur_by_date AS (
-    SELECT hl.data_date_id, hl.data_date, hl.loans_hashkey, ll.limit_hashkey
-    FROM hub_loans_active hl
-    INNER JOIN link_loans_limit_current_by_date ll
-        ON ll.data_date_id = hl.data_date_id AND ll.loans_hashkey = hl.loans_hashkey
-)</t>
-  </si>
-  <si>
-    <t>ll.data_date_id = hl.data_date_id AND ll.loans_hashkey = hl.loans_hashkey</t>
+    <t>ll.loans_hashkey = hl.loans_hashkey AND ll.source_event_date &lt;= hl.data_date (dedup link bang MAX_BY, 1 cot)</t>
+  </si>
+  <si>
+    <t>limit_sts_del_by_date AS (
+    SELECT ll.data_date_id, ll.limit_hashkey
+    FROM link_loans_limit_cur_by_date ll
+    JOIN IDENTIFIER(:cleaned || '.raw_vault.sts_hub_limit') sts
+        ON sts.limit_hashkey = ll.limit_hashkey AND sts.source_event_date &lt;= ll.data_date
+    GROUP BY ll.data_date_id, ll.limit_hashkey
+    HAVING max_by(sts.cdc_status, sts.source_event_date) = 'D'
+)</t>
+  </si>
+  <si>
+    <t>sts.limit_hashkey = ll.limit_hashkey AND sts.source_event_date &lt;= ll.data_date</t>
   </si>
   <si>
     <t>limit_active AS (
@@ -1277,25 +1305,29 @@
     FROM link_loans_limit_cur_by_date ll
     INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_limit') lim
         ON lim.limit_hashkey = ll.limit_hashkey
+    LEFT JOIN limit_sts_del_by_date d
+        ON d.data_date_id = ll.data_date_id AND d.limit_hashkey = ll.limit_hashkey
+    WHERE d.limit_hashkey IS NULL
 )</t>
   </si>
   <si>
     <t>lim</t>
   </si>
   <si>
-    <t>lim.limit_hashkey = ll.limit_hashkey</t>
-  </si>
-  <si>
-    <t>branch_limit AS (
-    SELECT l.data_date_id, l.unq_id_src_stm,
-        max_by(info.t_limit_currency, struct(info.source_event_date, info.load_timestamp, info.hashdiff)) AS schedule_currency,
-        CAST(NULL AS STRING) AS ar_nm,
-        CAST(TRY_TO_DATE(max_by(info.t_expiry_date, struct(info.source_event_date, info.load_timestamp, info.hashdiff)), 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
-        CAST(NULL AS DECIMAL(20,4)) AS shd_amount
+    <t>INNER JOIN / LEFT JOIN</t>
+  </si>
+  <si>
+    <t>lim: lim.limit_hashkey = ll.limit_hashkey | d: d.data_date_id = ll.data_date_id AND d.limit_hashkey = ll.limit_hashkey</t>
+  </si>
+  <si>
+    <t>sat_limit_latest AS (
+    -- FIX 2.2: 2 cot (&lt;=5) =&gt; MAX_BY thay QUALIFY ROW_NUMBER, GROUP BY theo khoa
+    SELECT l.data_date_id, l.data_date, l.unq_id_src_stm, l.limit_hashkey,
+        max_by(info.t_limit_currency, struct(info.source_event_date, info.load_timestamp)) AS t_limit_currency,
+        max_by(info.t_expiry_date, struct(info.source_event_date, info.load_timestamp)) AS t_expiry_date
     FROM limit_active l
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_limit_information') info
         ON info.limit_hashkey = l.limit_hashkey AND info.source_event_date &lt;= l.data_date
-    WHERE TRY_TO_DATE(info.t_expiry_date, 'yyyyMMdd') &gt; l.data_date
     GROUP BY l.data_date_id, l.data_date, l.unq_id_src_stm, l.limit_hashkey
 )</t>
   </si>
@@ -1306,27 +1338,87 @@
     <t>info.limit_hashkey = l.limit_hashkey AND info.source_event_date &lt;= l.data_date</t>
   </si>
   <si>
+    <t>branch_limit AS (
+    SELECT data_date_id, unq_id_src_stm, limit_hashkey AS ar_id,
+        t_limit_currency AS schedule_currency, CAST(NULL AS STRING) AS ar_nm,
+        CAST(TRY_TO_DATE(t_expiry_date, 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
+        CAST(NULL AS DECIMAL(20,4)) AS shd_amount
+    FROM sat_limit_latest
+    WHERE TRY_TO_DATE(t_expiry_date, 'yyyyMMdd') &gt; data_date
+)</t>
+  </si>
+  <si>
+    <t>AR_ID = limit_hashkey. Khong co SHD_AMT (luon NULL)</t>
+  </si>
+  <si>
+    <t>hub_consumer_loan_by_date AS (
+    SELECT c.data_date_id, c.data_date, h.consumer_loan_hashkey, h.business_key AS contractcode
+    FROM calendar_dates c
+    INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_consumer_loan') h
+        ON h.source_event_date &lt;= c.data_date
+)</t>
+  </si>
+  <si>
+    <t>next_payment_sts_del_by_date AS (
+    SELECT hc.data_date_id, hc.consumer_loan_hashkey
+    FROM hub_consumer_loan_by_date hc
+    JOIN IDENTIFIER(:cleaned || '.raw_vault.sts_hub_consumer_loan_next_payment_amount') sts
+        ON sts.consumer_loan_hashkey = hc.consumer_loan_hashkey AND sts.source_event_date &lt;= hc.data_date
+    GROUP BY hc.data_date_id, hc.consumer_loan_hashkey
+    HAVING max_by(sts.cdc_status, sts.source_event_date) = 'D'
+)</t>
+  </si>
+  <si>
+    <t>sts.consumer_loan_hashkey = hc.consumer_loan_hashkey AND sts.source_event_date &lt;= hc.data_date</t>
+  </si>
+  <si>
+    <t>hub_consumer_loan_active AS (
+    SELECT hc.data_date_id, hc.data_date, hc.consumer_loan_hashkey, hc.contractcode
+    FROM hub_consumer_loan_by_date hc
+    LEFT JOIN next_payment_sts_del_by_date d
+        ON d.data_date_id = hc.data_date_id AND d.consumer_loan_hashkey = hc.consumer_loan_hashkey
+    WHERE d.consumer_loan_hashkey IS NULL
+)</t>
+  </si>
+  <si>
+    <t>d.data_date_id = hc.data_date_id AND d.consumer_loan_hashkey = hc.consumer_loan_hashkey</t>
+  </si>
+  <si>
+    <t>sat_next_payment_latest AS (
+    -- FIX 2.2: 3 cot (&lt;=5) =&gt; MAX_BY thay QUALIFY ROW_NUMBER, GROUP BY theo khoa (giu ma_key trong GROUP BY nhu logic goc)
+    SELECT hc.data_date_id, hc.data_date, hc.consumer_loan_hashkey, hc.contractcode, s.ma_key,
+        max_by(s.duedate, struct(s.source_event_date, s.load_timestamp)) AS duedate,
+        max_by(s.principal, struct(s.source_event_date, s.load_timestamp)) AS principal,
+        max_by(s.remainprincipal, struct(s.source_event_date, s.load_timestamp)) AS remainprincipal
+    FROM hub_consumer_loan_active hc
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_next_payment_amount') s
+        ON s.consumer_loan_hashkey = hc.consumer_loan_hashkey AND s.source_event_date &lt;= hc.data_date
+    GROUP BY hc.data_date_id, hc.data_date, hc.consumer_loan_hashkey, hc.contractcode, s.ma_key
+)</t>
+  </si>
+  <si>
+    <t>s.consumer_loan_hashkey = hc.consumer_loan_hashkey AND s.source_event_date &lt;= hc.data_date</t>
+  </si>
+  <si>
     <t>branch_comb_next_payment AS (
-    SELECT c.data_date_id,
-        max_by(s.contractcode, struct(s.source_event_date, s.load_timestamp, s.hashdiff)) AS unq_id_src_stm,
-        CAST(NULL AS STRING) AS schedule_currency,
-        CAST(NULL AS STRING) AS ar_nm,
-        CAST(TRY_TO_DATE(max_by(s.duedate, struct(s.source_event_date, s.load_timestamp, s.hashdiff)), 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
-        CAST(max_by(s.principal, struct(s.source_event_date, s.load_timestamp, s.hashdiff)) AS DECIMAL(20,4)) AS shd_amount
-    FROM calendar_dates c
-    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_next_payment_amount') s
-        ON s.source_event_date &lt;= c.data_date
-    WHERE TRY_TO_DATE(s.duedate, 'yyyyMMdd') &gt; c.data_date
-      AND NVL(TRY_CAST(s.remainprincipal AS DECIMAL(20,4)), 0) &lt;&gt; 0
-    GROUP BY c.data_date_id, c.data_date, s.next_payment_amount_hashkey
-)</t>
-  </si>
-  <si>
-    <t>s.source_event_date &lt;= c.data_date</t>
-  </si>
-  <si>
-    <t>unioned_raw AS (UNION ALL 6 nhánh)
-unioned AS (GROUP BY + NVL(SUM(shd_amount), 0))</t>
+    SELECT data_date_id, contractcode AS unq_id_src_stm, consumer_loan_hashkey AS ar_id,
+        CAST(NULL AS STRING) AS schedule_currency, CAST(NULL AS STRING) AS ar_nm,
+        CAST(TRY_TO_DATE(duedate, 'yyyyMMdd') AS TIMESTAMP) AS shd_dt,
+        CAST(principal AS DECIMAL(20,4)) AS shd_amount
+    FROM sat_next_payment_latest
+    WHERE TRY_TO_DATE(duedate, 'yyyyMMdd') &gt; data_date
+      AND NVL(TRY_CAST(remainprincipal AS DECIMAL(20,4)), CAST(0 AS DECIMAL(20,4))) &lt;&gt; 0
+)</t>
+  </si>
+  <si>
+    <t>AR_ID = consumer_loan_hashkey. Loc remainprincipal &lt;&gt; 0 va duedate &gt; data_date</t>
+  </si>
+  <si>
+    <t>unioned_raw AS (UNION ALL 6 nhanh: LD_SCHEDULE, MD_DEAL, PAYMENT_DUE, PDPD, LIMIT, COMB_NEXT_PAYMENT)
+unioned AS (GROUP BY source_branch, data_date_id, unq_id_src_stm, ar_id, schedule_currency, ar_nm, shd_dt; NVL(SUM(shd_amount), 0))</t>
+  </si>
+  <si>
+    <t>Gop 6 nhanh + cong don SHD_AMT theo cung khoa</t>
   </si>
   <si>
     <t>FIELD MAPPING — V_LNSCHD_AVY</t>
@@ -1362,7 +1454,7 @@
     <t>Hardcode</t>
   </si>
   <si>
-    <t xml:space="preserve">CAST(NULL AS BIGINT) </t>
+    <t xml:space="preserve">unioned.ar_id  </t>
   </si>
   <si>
     <t>AVY_TP_ID</t>
@@ -1414,7 +1506,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1555,10 +1647,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
@@ -1793,53 +1881,53 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB0B0B0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1905,119 +1993,119 @@
     <xf numFmtId="20" fontId="20" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2388,23 +2476,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="42" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
     </row>
     <row r="2" spans="1:27" ht="9.75" customHeight="1">
       <c r="A2" s="2"/>
@@ -2425,26 +2513,26 @@
     </row>
     <row r="3" spans="1:27" ht="32.25" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="29" t="s">
+      <c r="L3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
     </row>
     <row r="4" spans="1:27" ht="12" customHeight="1">
       <c r="A4" s="2"/>
@@ -2465,30 +2553,30 @@
     </row>
     <row r="5" spans="1:27" ht="33.75" customHeight="1">
       <c r="A5" s="2"/>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="39" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="40" t="s">
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
       <c r="T5" s="5" t="s">
         <v>8</v>
       </c>
@@ -2502,198 +2590,198 @@
     </row>
     <row r="6" spans="1:27" ht="26.25" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
-      <c r="V6" s="45" t="s">
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="T6" s="38"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="W6" s="45"/>
-      <c r="X6" s="45"/>
-      <c r="Y6" s="45"/>
-      <c r="Z6" s="45"/>
-      <c r="AA6" s="45"/>
+      <c r="W6" s="39"/>
+      <c r="X6" s="39"/>
+      <c r="Y6" s="39"/>
+      <c r="Z6" s="39"/>
+      <c r="AA6" s="39"/>
     </row>
     <row r="7" spans="1:27" ht="21.75" customHeight="1">
       <c r="A7" s="2"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="45" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="W7" s="45"/>
-      <c r="X7" s="45"/>
-      <c r="Y7" s="45"/>
-      <c r="Z7" s="45"/>
-      <c r="AA7" s="47"/>
+      <c r="W7" s="39"/>
+      <c r="X7" s="39"/>
+      <c r="Y7" s="39"/>
+      <c r="Z7" s="39"/>
+      <c r="AA7" s="41"/>
     </row>
     <row r="8" spans="1:27" ht="20.25" customHeight="1">
       <c r="A8" s="2"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="T8" s="48"/>
-      <c r="U8" s="48"/>
-      <c r="V8" s="45" t="s">
+      <c r="T8" s="42"/>
+      <c r="U8" s="42"/>
+      <c r="V8" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="W8" s="45"/>
-      <c r="X8" s="45"/>
-      <c r="Y8" s="45"/>
-      <c r="Z8" s="45"/>
-      <c r="AA8" s="45"/>
+      <c r="W8" s="39"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="39"/>
     </row>
     <row r="9" spans="1:27" ht="18" customHeight="1">
       <c r="A9" s="2"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="40" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="41" t="s">
+      <c r="L9" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="42"/>
-      <c r="T9" s="52"/>
-      <c r="U9" s="52"/>
-      <c r="V9" s="45" t="s">
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="W9" s="45"/>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="45"/>
-      <c r="Z9" s="45"/>
-      <c r="AA9" s="45"/>
+      <c r="W9" s="39"/>
+      <c r="X9" s="39"/>
+      <c r="Y9" s="39"/>
+      <c r="Z9" s="39"/>
+      <c r="AA9" s="39"/>
     </row>
     <row r="10" spans="1:27" ht="21.75" customHeight="1">
       <c r="A10" s="2"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="45" t="s">
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="37"/>
+      <c r="T10" s="47"/>
+      <c r="U10" s="47"/>
+      <c r="V10" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="W10" s="45"/>
-      <c r="X10" s="45"/>
-      <c r="Y10" s="45"/>
-      <c r="Z10" s="45"/>
-      <c r="AA10" s="45"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="39"/>
+      <c r="Y10" s="39"/>
+      <c r="Z10" s="39"/>
+      <c r="AA10" s="39"/>
     </row>
     <row r="11" spans="1:27" ht="33.75" customHeight="1">
       <c r="A11" s="2"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="37"/>
     </row>
     <row r="12" spans="1:27" ht="15" customHeight="1">
       <c r="A12" s="2"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
     </row>
     <row r="13" spans="1:27" ht="33.75" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="T13" s="54" t="s">
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
+      <c r="T13" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="U13" s="55"/>
-      <c r="V13" s="56"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="50"/>
       <c r="W13" s="6" t="s">
         <v>16</v>
       </c>
@@ -2703,25 +2791,25 @@
     </row>
     <row r="14" spans="1:27" ht="33.75" customHeight="1">
       <c r="A14" s="2"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="T14" s="49" t="s">
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="37"/>
+      <c r="T14" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="U14" s="50"/>
-      <c r="V14" s="51"/>
+      <c r="U14" s="44"/>
+      <c r="V14" s="45"/>
       <c r="W14" s="7" t="s">
         <v>18</v>
       </c>
@@ -2731,54 +2819,54 @@
     </row>
     <row r="15" spans="1:27" ht="33.75" customHeight="1">
       <c r="A15" s="2"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
+      <c r="N15" s="37"/>
+      <c r="O15" s="37"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1">
       <c r="A16" s="2"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="37"/>
+      <c r="N16" s="37"/>
+      <c r="O16" s="37"/>
     </row>
     <row r="17" spans="1:15" ht="33.75" customHeight="1">
       <c r="A17" s="2"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
     </row>
     <row r="18" spans="1:15" ht="15.75" customHeight="1">
       <c r="A18" s="2"/>
@@ -2883,10 +2971,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4403BA20-9726-4447-B3A0-6A6E0C3105D6}">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="13" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" style="13" customWidth="1"/>
     <col min="2" max="2" width="86.42578125" style="16" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" style="13" customWidth="1"/>
     <col min="4" max="4" width="41" style="13" customWidth="1"/>
@@ -2896,13 +2984,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14" t="s">
@@ -2921,795 +3009,793 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="85.5" customHeight="1">
-      <c r="A3" s="21">
+    <row r="3" spans="1:5" ht="76.5" customHeight="1">
+      <c r="A3" s="53">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="56" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="88.5" customHeight="1">
-      <c r="A4" s="24">
+      <c r="A4" s="54">
         <v>2</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="58" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="117" customHeight="1">
-      <c r="A5" s="24">
+      <c r="A5" s="54">
         <v>3</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="58" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="113.25" customHeight="1">
-      <c r="A6" s="24">
+      <c r="A6" s="54">
         <v>4</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="58" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="119.25" customHeight="1">
-      <c r="A7" s="24">
+      <c r="A7" s="54">
         <v>5</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="58" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="109.5" customHeight="1">
-      <c r="A8" s="24">
+      <c r="A8" s="54">
         <v>6</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="58" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="124.5" customHeight="1">
-      <c r="A9" s="24">
+      <c r="A9" s="54">
         <v>7</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="58" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="105" customHeight="1">
-      <c r="A10" s="24">
+      <c r="A10" s="54">
         <v>8</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="150.75">
+      <c r="A11" s="54">
+        <v>9</v>
+      </c>
+      <c r="B11" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="58" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="141">
-      <c r="A11" s="24">
-        <v>9</v>
-      </c>
-      <c r="B11" s="25" t="s">
+      <c r="E11" s="58" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="147.75" customHeight="1">
+      <c r="A12" s="54">
+        <v>10</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="58" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="75.75">
+      <c r="A13" s="54">
+        <v>11</v>
+      </c>
+      <c r="B13" s="57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="58" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="120" customHeight="1">
+      <c r="A14" s="54">
+        <v>12</v>
+      </c>
+      <c r="B14" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="58" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="138" customHeight="1">
+      <c r="A15" s="54">
+        <v>13</v>
+      </c>
+      <c r="B15" s="57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="114" customHeight="1">
+      <c r="A16" s="54">
+        <v>14</v>
+      </c>
+      <c r="B16" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="58" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="148.5" customHeight="1">
+      <c r="A17" s="54">
+        <v>15</v>
+      </c>
+      <c r="B17" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="58" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="100.5">
+      <c r="A18" s="54">
+        <v>16</v>
+      </c>
+      <c r="B18" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="58" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="100.5">
+      <c r="A19" s="54">
+        <v>17</v>
+      </c>
+      <c r="B19" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="58" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="126.75" customHeight="1">
+      <c r="A20" s="54">
+        <v>18</v>
+      </c>
+      <c r="B20" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="88.5">
+      <c r="A21" s="54">
+        <v>19</v>
+      </c>
+      <c r="B21" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="26" t="s">
+    </row>
+    <row r="22" spans="1:5" ht="81.75" customHeight="1">
+      <c r="A22" s="54">
+        <v>20</v>
+      </c>
+      <c r="B22" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="D22" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="58" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="83.25" customHeight="1">
+      <c r="A23" s="54">
+        <v>21</v>
+      </c>
+      <c r="B23" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="58" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="147.75" customHeight="1">
-      <c r="A12" s="24">
-        <v>10</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="26" t="s">
+      <c r="D23" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="E23" s="58" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="43.5" customHeight="1">
+      <c r="A24" s="54">
+        <v>22</v>
+      </c>
+      <c r="B24" s="57" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="58" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="75.75">
+      <c r="A25" s="54">
+        <v>23</v>
+      </c>
+      <c r="B25" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="58" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="123.75" customHeight="1">
+      <c r="A26" s="54">
+        <v>24</v>
+      </c>
+      <c r="B26" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="58" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="88.5">
+      <c r="A27" s="54">
+        <v>25</v>
+      </c>
+      <c r="B27" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="D27" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="58" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="88.5" customHeight="1">
+      <c r="A28" s="54">
+        <v>26</v>
+      </c>
+      <c r="B28" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="58" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="171" customHeight="1">
+      <c r="A29" s="54">
+        <v>27</v>
+      </c>
+      <c r="B29" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="58" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="70.5">
-      <c r="A13" s="24">
-        <v>11</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="26" t="s">
+      <c r="E29" s="58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="202.5" customHeight="1">
+      <c r="A30" s="54">
+        <v>28</v>
+      </c>
+      <c r="B30" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="D30" s="58" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="120" customHeight="1">
-      <c r="A14" s="24">
-        <v>12</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="26" t="s">
+      <c r="E30" s="58" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="93.75" customHeight="1">
+      <c r="A31" s="54">
+        <v>29</v>
+      </c>
+      <c r="B31" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="58" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="125.25" customHeight="1">
+      <c r="A32" s="54">
+        <v>30</v>
+      </c>
+      <c r="B32" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="58" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="117" customHeight="1">
+      <c r="A33" s="54">
+        <v>31</v>
+      </c>
+      <c r="B33" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D33" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="58" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="172.5" customHeight="1">
+      <c r="A34" s="54">
+        <v>32</v>
+      </c>
+      <c r="B34" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="58" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="103.5" customHeight="1">
+      <c r="A35" s="54">
+        <v>33</v>
+      </c>
+      <c r="B35" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E35" s="58"/>
+    </row>
+    <row r="36" spans="1:5" ht="48" customHeight="1">
+      <c r="A36" s="54">
+        <v>34</v>
+      </c>
+      <c r="B36" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="58" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="138" customHeight="1">
-      <c r="A15" s="24">
-        <v>13</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="26" t="s">
+      <c r="D36" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="58" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="48" customHeight="1">
+      <c r="A37" s="54">
+        <v>35</v>
+      </c>
+      <c r="B37" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="58" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="114" customHeight="1">
-      <c r="A16" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="26" t="s">
+      <c r="E37" s="58" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="48" customHeight="1">
+      <c r="A38" s="54">
+        <v>36</v>
+      </c>
+      <c r="B38" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D38" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="148.5" customHeight="1">
-      <c r="A17" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="E38" s="58" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="48" customHeight="1">
+      <c r="A39" s="54">
+        <v>37</v>
+      </c>
+      <c r="B39" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="E39" s="58" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="135.75" customHeight="1">
+      <c r="A40" s="54">
+        <v>38</v>
+      </c>
+      <c r="B40" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="58" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="120.75" customHeight="1">
+      <c r="A41" s="54">
+        <v>39</v>
+      </c>
+      <c r="B41" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D41" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="58" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="63.75" customHeight="1">
+      <c r="A42" s="54">
+        <v>40</v>
+      </c>
+      <c r="B42" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" s="58" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="63.75" customHeight="1">
+      <c r="A43" s="54">
+        <v>41</v>
+      </c>
+      <c r="B43" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="58" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="63.75" customHeight="1">
+      <c r="A44" s="54">
+        <v>42</v>
+      </c>
+      <c r="B44" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="26" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="93.75">
-      <c r="A18" s="24">
-        <v>15</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="26" t="s">
+      <c r="E44" s="58" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="63.75" customHeight="1">
+      <c r="A45" s="54">
+        <v>43</v>
+      </c>
+      <c r="B45" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="C45" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="26" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="93.75">
-      <c r="A19" s="24">
-        <v>16</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="26" t="s">
+      <c r="E45" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="63.75" customHeight="1">
+      <c r="A46" s="54">
+        <v>44</v>
+      </c>
+      <c r="B46" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="58" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="63.75" customHeight="1">
+      <c r="A47" s="54">
         <v>45</v>
       </c>
-      <c r="E19" s="26" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="126.75" customHeight="1">
-      <c r="A20" s="24">
-        <v>17</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="82.5">
-      <c r="A21" s="24">
-        <v>18</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="26" t="s">
+      <c r="B47" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="D47" s="58" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="81.75" customHeight="1">
-      <c r="A22" s="24">
-        <v>19</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="83.25" customHeight="1">
-      <c r="A23" s="24">
+      <c r="E47" s="58" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="43.5" customHeight="1">
-      <c r="A24" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="70.5">
-      <c r="A25" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="123.75" customHeight="1">
-      <c r="A26" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="82.5">
-      <c r="A27" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="88.5" customHeight="1">
-      <c r="A28" s="24">
-        <v>23</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="171" customHeight="1">
-      <c r="A29" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="202.5" customHeight="1">
-      <c r="A30" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="B30" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="93.75" customHeight="1">
-      <c r="A31" s="24">
-        <v>25</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="48" customHeight="1">
-      <c r="A32" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="48" customHeight="1">
-      <c r="A33" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="48" customHeight="1">
-      <c r="A34" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="48" customHeight="1">
-      <c r="A35" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="B35" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="48" customHeight="1">
-      <c r="A36" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="C36" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="48" customHeight="1">
-      <c r="A37" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C37" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="48" customHeight="1">
-      <c r="A38" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B38" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C38" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="48" customHeight="1">
-      <c r="A39" s="24">
-        <v>28</v>
-      </c>
-      <c r="B39" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C39" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" s="26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="135.75" customHeight="1">
-      <c r="A40" s="24">
-        <v>29</v>
-      </c>
-      <c r="B40" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="C40" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="120.75" customHeight="1">
-      <c r="A41" s="24">
-        <v>30</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="C41" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D41" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="63.75" customHeight="1">
-      <c r="A42" s="24">
-        <v>31</v>
-      </c>
-      <c r="B42" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="C42" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="58" t="s">
-        <v>134</v>
-      </c>
-      <c r="B43" s="58"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="19" t="s">
+      <c r="B49" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="C49" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D45" s="20">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E45" s="19" t="s">
+      <c r="D49" s="17" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="19" t="s">
+      <c r="E49" s="17" t="s">
         <v>142</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E47" s="19">
-        <v>101500001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D48" s="20">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D49" s="20">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -3717,16 +3803,16 @@
         <v>6</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D50" s="20">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -3734,16 +3820,16 @@
         <v>6</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -3751,28 +3837,123 @@
         <v>6</v>
       </c>
       <c r="B52" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E52" s="19">
+        <v>101500001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D53" s="20">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D54" s="20">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D55" s="20">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="C52" s="19" t="s">
+      <c r="C56" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="D52" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="E52" s="19" t="s">
+      <c r="D56" s="19" t="s">
         <v>160</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A48:E48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -3944,7 +4125,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3953,24 +4134,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5A42734-B7D6-4361-97F0-D33E553F5AE0}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C0D205A-D2F1-4B7A-B689-C91A2C67079A}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0F00C7-FB04-4E97-835E-CF38CB03559A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5A42734-B7D6-4361-97F0-D33E553F5AE0}"/>
 </file>